--- a/01-your-first-py-cell-solutions.xlsx
+++ b/01-your-first-py-cell-solutions.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="32">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -137,8 +137,87 @@
       <color rgb="002E7D2E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00718096"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A202C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002A4365"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00C53030"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001A202C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="002F6E2F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C53030"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A202C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="002F6E2F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -175,8 +254,38 @@
         <bgColor rgb="00E6F3E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A4365"/>
+        <bgColor rgb="002A4365"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1EFE8"/>
+        <bgColor rgb="00F1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF0F5"/>
+        <bgColor rgb="00EDF0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7E7"/>
+        <bgColor rgb="00FCE7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F1E7"/>
+        <bgColor rgb="00E7F1E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -241,11 +350,67 @@
       </bottom>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00D8DAE0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DAE0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DAE0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DAE0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00C53030"/>
+      </left>
+      <right style="medium">
+        <color rgb="00C53030"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C53030"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C53030"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002A4365"/>
+      </left>
+      <right style="medium">
+        <color rgb="002A4365"/>
+      </right>
+      <top style="medium">
+        <color rgb="002A4365"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002A4365"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F6E2F"/>
+      </left>
+      <right style="medium">
+        <color rgb="002F6E2F"/>
+      </right>
+      <top style="medium">
+        <color rgb="002F6E2F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002F6E2F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,6 +479,49 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,7 +916,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00CF3338"/>
+    <tabColor rgb="002A4365"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -723,53 +931,46 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>Answer key — Your first PY() cell</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>This workbook teaches ONE lesson: where you place a PY() cell on the grid matters. Switch to the hello-world tab and follow the three steps below, in order. Steps 1 and 2 will work. Step 3 will fail — on purpose. That's the lesson.</t>
+      <c r="B2" s="31" t="inlineStr">
+        <is>
+          <t>ANSWER KEY: each cell below shows the expected result on the hello-world tab. Open the unsolved version of this workbook to do the steps yourself.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>To insert a PY() cell:  Ctrl + Alt + Shift + P  (or Formulas tab → Insert Python)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>✓  ANSWER KEY</t>
-        </is>
-      </c>
-    </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Step 1 — Define a variable</t>
         </is>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>In cell B2 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>my_object = 'Hello, world!'
 my_object</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>→ runs successfully. Shows 'Hello, world!' (as Python Object).</t>
         </is>
@@ -777,24 +978,24 @@
     </row>
     <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Step 2 — Reference it BELOW &amp; RIGHT</t>
         </is>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>In cell C3 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>my_object</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>→ works. Python in Excel runs B2 first (above C3 in calc order), so my_object exists when C3 runs.</t>
         </is>
@@ -802,24 +1003,24 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Step 3 — Reference it ABOVE — fails</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>In cell A1 on the hello-world tab</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>my_object</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>→ FAILS with #PYTHON. A1 runs before B2 in calc order, so my_object doesn't exist yet. This is the gotcha.</t>
         </is>
@@ -827,14 +1028,14 @@
     </row>
     <row r="13" ht="8" customHeight="1"/>
     <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>✓  Takeaway</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>Python in Excel reads cells left-to-right, top-to-bottom — like reading a page. Put your definitions (imports, variables) in the top-left of the sheet and build DOWN and RIGHT. When you see #PYTHON on a cell that references a variable, check whether the cell DEFINING that variable is above or to the left of where you're using it.</t>
         </is>
@@ -859,7 +1060,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E7D2E"/>
+    <tabColor rgb="002F6E2F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -874,7 +1075,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>PY cell:  my_object
 result:  #PYTHON</t>
@@ -882,7 +1083,7 @@
       </c>
       <c r="B1" s="22" t="n"/>
       <c r="C1" s="22" t="n"/>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>← Step 3: A1 references my_object BEFORE B2 has defined it → #PYTHON</t>
         </is>
@@ -890,14 +1091,14 @@
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="22" t="n"/>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>PY cell:  my_object = 'Hello, world!'
 result:  'Hello, world!'</t>
         </is>
       </c>
       <c r="C2" s="22" t="n"/>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>← Step 1: B2 defines my_object</t>
         </is>
@@ -906,13 +1107,13 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="22" t="n"/>
       <c r="B3" s="22" t="n"/>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>PY cell:  my_object
 result:  'Hello, world!'</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>← Step 2: C3 references my_object AFTER B2 has defined it → works</t>
         </is>
@@ -925,7 +1126,7 @@
       <c r="D4" s="22" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>How to read this answer key:</t>
         </is>
@@ -935,28 +1136,28 @@
       <c r="D5" s="22" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Each colored cell above shows what would be in a PY() cell at that location, plus what it would return.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>When you type the code into your own PY() cell, you don't type 'PY cell:' or 'result:' — just the code itself.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>A1 fails because Python in Excel runs cells in reading order: A1 → B2 → C3. When A1 runs, my_object hasn't been defined yet.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>C3 works because by the time it runs, B2 has already defined my_object.</t>
         </is>
